--- a/marketing_report/outputs/Posgrados/Analisis_UTM/analisis_utm_completo.xlsx
+++ b/marketing_report/outputs/Posgrados/Analisis_UTM/analisis_utm_completo.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,18 +470,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ig</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -496,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +578,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14909096324</t>
+          <t>120235998797960048</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -569,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -578,7 +600,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15042792606</t>
+          <t>14875022827</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -600,7 +622,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15360035696</t>
+          <t>14893252513</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -622,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15767139553</t>
+          <t>14909096324</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -635,7 +657,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>100</v>
@@ -644,22 +666,110 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>15042792606</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15360035696</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15767139553</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>21676468921</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>21772187688</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>100</v>
       </c>
     </row>
@@ -674,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,18 +826,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -774,13 +906,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -790,13 +922,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -806,13 +938,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/marketing_report/outputs/Posgrados/Analisis_UTM/analisis_utm_completo.xlsx
+++ b/marketing_report/outputs/Posgrados/Analisis_UTM/analisis_utm_completo.xlsx
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,6 +770,28 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>23220287690</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>100</v>
       </c>
     </row>
@@ -826,16 +848,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -909,10 +931,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -922,13 +944,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -941,10 +963,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/marketing_report/outputs/Posgrados/Analisis_UTM/analisis_utm_completo.xlsx
+++ b/marketing_report/outputs/Posgrados/Analisis_UTM/analisis_utm_completo.xlsx
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
         <v>11</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" t="n">
-        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,20 +556,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14876203835</t>
+          <t>120235998797960048</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -578,7 +578,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>120235998797960048</t>
+          <t>14875022827</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -600,7 +600,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14875022827</t>
+          <t>14876203835</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -732,7 +732,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21676468921</t>
+          <t>21772187688</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -754,7 +754,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21772187688</t>
+          <t>23220287690</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -770,28 +770,6 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>23220287690</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
         <v>100</v>
       </c>
     </row>
@@ -848,16 +826,16 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
         <v>11</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" t="n">
-        <v>11</v>
-      </c>
-      <c r="E2" t="n">
-        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -931,10 +909,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -944,13 +922,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -963,10 +941,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
